--- a/SD.xlsx
+++ b/SD.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://fnsul-my.sharepoint.com/personal/jungbin_lee_fnsusa_com/Documents/바탕 화면/code/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="65" documentId="8_{17F6C150-52D1-4709-B32B-2081CAA0F213}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CAD0986D-1990-4F73-833C-225B8AC90E42}"/>
+  <xr:revisionPtr revIDLastSave="93" documentId="8_{17F6C150-52D1-4709-B32B-2081CAA0F213}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{080484AC-1FF0-4CA5-98F7-5845063375F6}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{CE368B0D-5E19-4AE2-AF1A-E02F0281253F}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="36">
   <si>
     <t>SD-3</t>
   </si>
@@ -141,6 +141,12 @@
   </si>
   <si>
     <t>SD0</t>
+  </si>
+  <si>
+    <t>SDE-0</t>
+  </si>
+  <si>
+    <t>051203_1N</t>
   </si>
 </sst>
 </file>
@@ -517,7 +523,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8883645C-3432-47A1-B329-9577D994FDF6}">
-  <dimension ref="A1:C30"/>
+  <dimension ref="A1:C31"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
@@ -533,7 +539,7 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>2520</v>
+        <v>2580</v>
       </c>
       <c r="C2">
         <v>2625</v>
@@ -543,283 +549,291 @@
       <c r="A3" t="s">
         <v>2</v>
       </c>
+      <c r="B3">
+        <v>2527</v>
+      </c>
+      <c r="C3">
+        <v>2520</v>
+      </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>33</v>
       </c>
-      <c r="B4">
-        <v>904</v>
-      </c>
       <c r="C4">
-        <v>2530</v>
+        <v>2573</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>3</v>
       </c>
-      <c r="B5">
-        <v>2230</v>
+      <c r="C5">
+        <v>2530</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>4</v>
-      </c>
-      <c r="B6" t="s">
-        <v>32</v>
+        <v>34</v>
+      </c>
+      <c r="B6">
+        <v>2230</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B7">
-        <v>2611</v>
-      </c>
-      <c r="C7">
-        <v>2603</v>
+        <v>2619</v>
+      </c>
+      <c r="C7" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B8">
-        <v>1209</v>
+        <v>2611</v>
       </c>
       <c r="C8">
-        <v>2140</v>
+        <v>2603</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B9">
-        <v>2606</v>
+        <v>1209</v>
       </c>
       <c r="C9">
-        <v>2531</v>
+        <v>2140</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B10">
-        <v>905</v>
+        <v>2606</v>
       </c>
       <c r="C10">
-        <v>2599</v>
+        <v>2531</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>10</v>
-      </c>
-      <c r="B11">
-        <v>2597</v>
-      </c>
-      <c r="C11">
-        <v>2604</v>
+        <v>8</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B12">
-        <v>2130</v>
+        <v>2599</v>
+      </c>
+      <c r="C12">
+        <v>2604</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B13">
-        <v>2333</v>
-      </c>
-      <c r="C13">
-        <v>2124</v>
+        <v>2130</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B14">
-        <v>363</v>
+        <v>905</v>
       </c>
       <c r="C14">
-        <v>2173</v>
+        <v>2646</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B15">
-        <v>2607</v>
+        <v>363</v>
       </c>
       <c r="C15">
-        <v>2553</v>
+        <v>2173</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>14</v>
-      </c>
-      <c r="B16">
-        <v>1159</v>
-      </c>
-      <c r="C16" t="s">
-        <v>31</v>
+        <v>13</v>
+      </c>
+      <c r="B16" t="s">
+        <v>35</v>
+      </c>
+      <c r="C16">
+        <v>2608</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B17">
-        <v>2118</v>
-      </c>
-      <c r="C17">
-        <v>2502</v>
+        <v>1159</v>
+      </c>
+      <c r="C17" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B18">
-        <v>2593</v>
+        <v>2118</v>
       </c>
       <c r="C18">
-        <v>2576</v>
+        <v>2502</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B19">
-        <v>2551</v>
+        <v>2649</v>
       </c>
       <c r="C19">
-        <v>2482</v>
+        <v>2578</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>18</v>
-      </c>
-      <c r="B20" t="s">
-        <v>30</v>
+        <v>17</v>
+      </c>
+      <c r="B20">
+        <v>2551</v>
       </c>
       <c r="C20">
-        <v>2378</v>
+        <v>2412</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>19</v>
-      </c>
-      <c r="B21">
-        <v>2511</v>
+        <v>18</v>
+      </c>
+      <c r="B21" t="s">
+        <v>30</v>
+      </c>
+      <c r="C21">
+        <v>2378</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B22">
-        <v>2622</v>
-      </c>
-      <c r="C22">
-        <v>2583</v>
+        <v>2511</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B23">
-        <v>1287</v>
+        <v>2622</v>
       </c>
       <c r="C23">
-        <v>2515</v>
+        <v>2583</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>22</v>
-      </c>
-      <c r="B24" t="s">
-        <v>29</v>
+        <v>21</v>
+      </c>
+      <c r="B24">
+        <v>1287</v>
       </c>
       <c r="C24">
-        <v>2225</v>
+        <v>2515</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>23</v>
-      </c>
-      <c r="B25">
-        <v>2141</v>
+        <v>22</v>
+      </c>
+      <c r="B25" t="s">
+        <v>29</v>
       </c>
       <c r="C25">
-        <v>2577</v>
+        <v>2225</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B26">
-        <v>2600</v>
+        <v>2141</v>
+      </c>
+      <c r="C26">
+        <v>2577</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B27">
-        <v>2143</v>
-      </c>
-      <c r="C27">
-        <v>2538</v>
+        <v>2600</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B28">
-        <v>2627</v>
+        <v>2143</v>
       </c>
       <c r="C28">
-        <v>2589</v>
+        <v>2538</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B29">
-        <v>2626</v>
+        <v>2627</v>
       </c>
       <c r="C29">
-        <v>2554</v>
+        <v>2589</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
+        <v>27</v>
+      </c>
+      <c r="B30">
+        <v>2594</v>
+      </c>
+      <c r="C30">
+        <v>2634</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
         <v>28</v>
       </c>
-      <c r="B30">
+      <c r="B31">
         <v>2518</v>
       </c>
     </row>

--- a/SD.xlsx
+++ b/SD.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://fnsul-my.sharepoint.com/personal/jungbin_lee_fnsusa_com/Documents/바탕 화면/code/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="93" documentId="8_{17F6C150-52D1-4709-B32B-2081CAA0F213}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{080484AC-1FF0-4CA5-98F7-5845063375F6}"/>
+  <xr:revisionPtr revIDLastSave="174" documentId="8_{17F6C150-52D1-4709-B32B-2081CAA0F213}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1613EC75-00D4-4A58-8D22-0D8DB12B7916}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{CE368B0D-5E19-4AE2-AF1A-E02F0281253F}"/>
   </bookViews>
@@ -128,12 +128,6 @@
     <t>SDX1</t>
   </si>
   <si>
-    <t>81205_1N</t>
-  </si>
-  <si>
-    <t>81002_1K</t>
-  </si>
-  <si>
     <t>91006_1A</t>
   </si>
   <si>
@@ -146,7 +140,13 @@
     <t>SDE-0</t>
   </si>
   <si>
-    <t>051203_1N</t>
+    <t>31004_1G</t>
+  </si>
+  <si>
+    <t>OUTPUT STATION</t>
+  </si>
+  <si>
+    <t>51001_1G</t>
   </si>
 </sst>
 </file>
@@ -523,61 +523,46 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8883645C-3432-47A1-B329-9577D994FDF6}">
-  <dimension ref="A1:C31"/>
+  <dimension ref="A1:C32"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="C1">
-        <v>2444</v>
-      </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>1</v>
       </c>
-      <c r="B2">
-        <v>2580</v>
-      </c>
-      <c r="C2">
-        <v>2625</v>
-      </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>2</v>
       </c>
-      <c r="B3">
-        <v>2527</v>
-      </c>
       <c r="C3">
         <v>2520</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>33</v>
+        <v>31</v>
+      </c>
+      <c r="B4">
+        <v>2569</v>
       </c>
       <c r="C4">
-        <v>2573</v>
+        <v>2527</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>3</v>
       </c>
-      <c r="C5">
-        <v>2530</v>
-      </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>34</v>
-      </c>
-      <c r="B6">
-        <v>2230</v>
+        <v>32</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
@@ -585,40 +570,28 @@
         <v>4</v>
       </c>
       <c r="B7">
-        <v>2619</v>
+        <v>2584</v>
       </c>
       <c r="C7" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>5</v>
       </c>
-      <c r="B8">
-        <v>2611</v>
-      </c>
-      <c r="C8">
-        <v>2603</v>
-      </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>6</v>
       </c>
-      <c r="B9">
-        <v>1209</v>
-      </c>
-      <c r="C9">
-        <v>2140</v>
-      </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>7</v>
       </c>
       <c r="B10">
-        <v>2606</v>
+        <v>2617</v>
       </c>
       <c r="C10">
         <v>2531</v>
@@ -628,46 +601,34 @@
       <c r="A11" t="s">
         <v>8</v>
       </c>
+      <c r="C11">
+        <v>2679</v>
+      </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>10</v>
       </c>
-      <c r="B12">
-        <v>2599</v>
-      </c>
-      <c r="C12">
-        <v>2604</v>
-      </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>9</v>
       </c>
-      <c r="B13">
-        <v>2130</v>
-      </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>11</v>
       </c>
-      <c r="B14">
-        <v>905</v>
-      </c>
-      <c r="C14">
-        <v>2646</v>
-      </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>12</v>
       </c>
       <c r="B15">
-        <v>363</v>
+        <v>2723</v>
       </c>
       <c r="C15">
-        <v>2173</v>
+        <v>2700</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.3">
@@ -675,10 +636,10 @@
         <v>13</v>
       </c>
       <c r="B16" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C16">
-        <v>2608</v>
+        <v>2709</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
@@ -686,10 +647,10 @@
         <v>14</v>
       </c>
       <c r="B17">
-        <v>1159</v>
+        <v>2733</v>
       </c>
       <c r="C17" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
@@ -697,21 +658,18 @@
         <v>15</v>
       </c>
       <c r="B18">
-        <v>2118</v>
+        <v>2579</v>
       </c>
       <c r="C18">
-        <v>2502</v>
+        <v>2645</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>16</v>
       </c>
-      <c r="B19">
-        <v>2649</v>
-      </c>
       <c r="C19">
-        <v>2578</v>
+        <v>2708</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
@@ -719,21 +677,21 @@
         <v>17</v>
       </c>
       <c r="B20">
-        <v>2551</v>
+        <v>2744</v>
       </c>
       <c r="C20">
-        <v>2412</v>
+        <v>2769</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>18</v>
       </c>
-      <c r="B21" t="s">
-        <v>30</v>
+      <c r="B21">
+        <v>2764</v>
       </c>
       <c r="C21">
-        <v>2378</v>
+        <v>2551</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.3">
@@ -748,11 +706,11 @@
       <c r="A23" t="s">
         <v>20</v>
       </c>
-      <c r="B23">
-        <v>2622</v>
+      <c r="B23" t="s">
+        <v>35</v>
       </c>
       <c r="C23">
-        <v>2583</v>
+        <v>2748</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.3">
@@ -770,11 +728,11 @@
       <c r="A25" t="s">
         <v>22</v>
       </c>
-      <c r="B25" t="s">
-        <v>29</v>
+      <c r="B25">
+        <v>2782</v>
       </c>
       <c r="C25">
-        <v>2225</v>
+        <v>2686</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.3">
@@ -782,10 +740,10 @@
         <v>23</v>
       </c>
       <c r="B26">
-        <v>2141</v>
+        <v>2763</v>
       </c>
       <c r="C26">
-        <v>2577</v>
+        <v>2770</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.3">
@@ -793,48 +751,47 @@
         <v>24</v>
       </c>
       <c r="B27">
-        <v>2600</v>
+        <v>2772</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>26</v>
-      </c>
-      <c r="B28">
-        <v>2143</v>
-      </c>
-      <c r="C28">
-        <v>2538</v>
+        <v>34</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B29">
-        <v>2627</v>
+        <v>2693</v>
       </c>
       <c r="C29">
-        <v>2589</v>
+        <v>2538</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B30">
-        <v>2594</v>
+        <v>2665</v>
       </c>
       <c r="C30">
-        <v>2634</v>
+        <v>2760</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
         <v>28</v>
       </c>
-      <c r="B31">
-        <v>2518</v>
+      <c r="C32">
+        <v>2695</v>
       </c>
     </row>
   </sheetData>

--- a/SD.xlsx
+++ b/SD.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://fnsul-my.sharepoint.com/personal/jungbin_lee_fnsusa_com/Documents/바탕 화면/code/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="174" documentId="8_{17F6C150-52D1-4709-B32B-2081CAA0F213}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1613EC75-00D4-4A58-8D22-0D8DB12B7916}"/>
+  <xr:revisionPtr revIDLastSave="214" documentId="8_{17F6C150-52D1-4709-B32B-2081CAA0F213}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4B7DB03A-B08C-445D-88E5-02C1BA338096}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{CE368B0D-5E19-4AE2-AF1A-E02F0281253F}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="34">
   <si>
     <t>SD-3</t>
   </si>
@@ -113,9 +113,6 @@
     <t>SD19</t>
   </si>
   <si>
-    <t>NEW WATRERPROOF</t>
-  </si>
-  <si>
     <t>SDE-3</t>
   </si>
   <si>
@@ -140,13 +137,10 @@
     <t>SDE-0</t>
   </si>
   <si>
-    <t>31004_1G</t>
-  </si>
-  <si>
     <t>OUTPUT STATION</t>
   </si>
   <si>
-    <t>51001_1G</t>
+    <t>NEW WATERPROOF</t>
   </si>
 </sst>
 </file>
@@ -541,39 +535,33 @@
         <v>2</v>
       </c>
       <c r="C3">
-        <v>2520</v>
+        <v>2760</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>31</v>
-      </c>
-      <c r="B4">
-        <v>2569</v>
-      </c>
-      <c r="C4">
-        <v>2527</v>
+        <v>30</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>3</v>
       </c>
+      <c r="C5">
+        <v>2527</v>
+      </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>4</v>
       </c>
-      <c r="B7">
-        <v>2584</v>
-      </c>
       <c r="C7" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
@@ -590,9 +578,6 @@
       <c r="A10" t="s">
         <v>7</v>
       </c>
-      <c r="B10">
-        <v>2617</v>
-      </c>
       <c r="C10">
         <v>2531</v>
       </c>
@@ -614,6 +599,9 @@
       <c r="A13" t="s">
         <v>9</v>
       </c>
+      <c r="B13">
+        <v>2444</v>
+      </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
@@ -624,22 +612,16 @@
       <c r="A15" t="s">
         <v>12</v>
       </c>
-      <c r="B15">
-        <v>2723</v>
-      </c>
       <c r="C15">
-        <v>2700</v>
+        <v>2616</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>13</v>
       </c>
-      <c r="B16" t="s">
-        <v>33</v>
-      </c>
       <c r="C16">
-        <v>2709</v>
+        <v>2773</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
@@ -647,29 +629,26 @@
         <v>14</v>
       </c>
       <c r="B17">
-        <v>2733</v>
+        <v>2579</v>
       </c>
       <c r="C17" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>15</v>
       </c>
-      <c r="B18">
-        <v>2579</v>
-      </c>
-      <c r="C18">
-        <v>2645</v>
-      </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>16</v>
       </c>
+      <c r="B19">
+        <v>2746</v>
+      </c>
       <c r="C19">
-        <v>2708</v>
+        <v>2790</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
@@ -677,19 +656,16 @@
         <v>17</v>
       </c>
       <c r="B20">
-        <v>2744</v>
+        <v>2589</v>
       </c>
       <c r="C20">
-        <v>2769</v>
+        <v>2725</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>18</v>
       </c>
-      <c r="B21">
-        <v>2764</v>
-      </c>
       <c r="C21">
         <v>2551</v>
       </c>
@@ -706,11 +682,8 @@
       <c r="A23" t="s">
         <v>20</v>
       </c>
-      <c r="B23" t="s">
-        <v>35</v>
-      </c>
       <c r="C23">
-        <v>2748</v>
+        <v>2726</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.3">
@@ -718,7 +691,7 @@
         <v>21</v>
       </c>
       <c r="B24">
-        <v>1287</v>
+        <v>2795</v>
       </c>
       <c r="C24">
         <v>2515</v>
@@ -729,7 +702,7 @@
         <v>22</v>
       </c>
       <c r="B25">
-        <v>2782</v>
+        <v>2800</v>
       </c>
       <c r="C25">
         <v>2686</v>
@@ -740,28 +713,25 @@
         <v>23</v>
       </c>
       <c r="B26">
-        <v>2763</v>
+        <v>2758</v>
       </c>
       <c r="C26">
-        <v>2770</v>
+        <v>2793</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>24</v>
-      </c>
-      <c r="B27">
-        <v>2772</v>
+        <v>33</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B29">
         <v>2693</v>
@@ -772,23 +742,23 @@
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>25</v>
-      </c>
-      <c r="B30">
-        <v>2665</v>
-      </c>
-      <c r="C30">
-        <v>2760</v>
+        <v>24</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>27</v>
+        <v>26</v>
+      </c>
+      <c r="B31">
+        <v>2811</v>
+      </c>
+      <c r="C31">
+        <v>2791</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C32">
         <v>2695</v>
